--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>58.0064</v>
+      </c>
+      <c r="C2">
+        <v>94.07301</v>
+      </c>
+      <c r="D2">
+        <v>82.60173</v>
+      </c>
+      <c r="E2">
+        <v>41.76839</v>
+      </c>
+      <c r="F2">
         <v>58.15052</v>
       </c>
-      <c r="C2">
-        <v>58.0064</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>98.37719</v>
       </c>
-      <c r="E2">
-        <v>94.07301</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>102.4031</v>
       </c>
-      <c r="G2">
-        <v>82.60173</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>63.86795</v>
-      </c>
-      <c r="I2">
-        <v>41.76839</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>72.29917</v>
+      </c>
+      <c r="C3">
+        <v>96.86494999999999</v>
+      </c>
+      <c r="D3">
+        <v>82.40495</v>
+      </c>
+      <c r="E3">
+        <v>39.90676</v>
+      </c>
+      <c r="F3">
         <v>72.43768</v>
       </c>
-      <c r="C3">
-        <v>72.29917</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>101.246</v>
       </c>
-      <c r="E3">
-        <v>96.86494999999999</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>101.8568</v>
       </c>
-      <c r="G3">
-        <v>82.40495</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>61.58508</v>
-      </c>
-      <c r="I3">
-        <v>39.90676</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>63.83154</v>
+      </c>
+      <c r="C4">
+        <v>95.60209999999999</v>
+      </c>
+      <c r="D4">
+        <v>82.72059</v>
+      </c>
+      <c r="E4">
+        <v>24.95298</v>
+      </c>
+      <c r="F4">
         <v>63.91412</v>
       </c>
-      <c r="C4">
-        <v>63.83154</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>100.1571</v>
       </c>
-      <c r="E4">
-        <v>95.60209999999999</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>107.8431</v>
       </c>
-      <c r="G4">
-        <v>82.72059</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>34.98433</v>
-      </c>
-      <c r="I4">
-        <v>24.95298</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>61.97866</v>
+      </c>
+      <c r="C5">
+        <v>95.44902999999999</v>
+      </c>
+      <c r="D5">
+        <v>85.57807</v>
+      </c>
+      <c r="E5">
+        <v>36.72026</v>
+      </c>
+      <c r="F5">
         <v>62.17265</v>
       </c>
-      <c r="C5">
-        <v>61.97866</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>100.3641</v>
       </c>
-      <c r="E5">
-        <v>95.44902999999999</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>97.61621</v>
       </c>
-      <c r="G5">
-        <v>85.57807</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>58.5209</v>
-      </c>
-      <c r="I5">
-        <v>36.72026</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>64.32161000000001</v>
+      </c>
+      <c r="C6">
+        <v>96.03907</v>
+      </c>
+      <c r="D6">
+        <v>87.7426</v>
+      </c>
+      <c r="E6">
+        <v>41.9661</v>
+      </c>
+      <c r="F6">
         <v>64.42211</v>
       </c>
-      <c r="C6">
-        <v>64.32161000000001</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>100.1085</v>
       </c>
-      <c r="E6">
-        <v>96.03907</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>108.2738</v>
       </c>
-      <c r="G6">
-        <v>87.7426</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>65.35593</v>
-      </c>
-      <c r="I6">
-        <v>41.9661</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>65.31044</v>
+      </c>
+      <c r="C7">
+        <v>96.48519</v>
+      </c>
+      <c r="D7">
+        <v>87.6408</v>
+      </c>
+      <c r="E7">
+        <v>41.18818</v>
+      </c>
+      <c r="F7">
         <v>65.54562</v>
       </c>
-      <c r="C7">
-        <v>65.31044</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>99.35686</v>
       </c>
-      <c r="E7">
-        <v>96.48519</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>104.1615</v>
       </c>
-      <c r="G7">
-        <v>87.6408</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>60.05642</v>
-      </c>
-      <c r="I7">
-        <v>41.18818</v>
       </c>
     </row>
     <row r="8">
@@ -597,25 +597,25 @@
         <v>63.34232</v>
       </c>
       <c r="C8">
+        <v>95.79684</v>
+      </c>
+      <c r="D8">
+        <v>88.50574</v>
+      </c>
+      <c r="E8">
+        <v>33.41837</v>
+      </c>
+      <c r="F8">
         <v>63.34232</v>
       </c>
-      <c r="D8">
+      <c r="G8">
         <v>98.94920999999999</v>
       </c>
-      <c r="E8">
-        <v>95.79684</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>102.2989</v>
       </c>
-      <c r="G8">
-        <v>88.50574</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>47.70408</v>
-      </c>
-      <c r="I8">
-        <v>33.41837</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>71.42856999999999</v>
+      </c>
+      <c r="C9">
+        <v>95.83333</v>
+      </c>
+      <c r="D9">
+        <v>85.49223000000001</v>
+      </c>
+      <c r="E9">
+        <v>33.96482</v>
+      </c>
+      <c r="F9">
         <v>71.7728</v>
       </c>
-      <c r="C9">
-        <v>71.42856999999999</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>99.88739</v>
       </c>
-      <c r="E9">
-        <v>95.83333</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>114.5078</v>
       </c>
-      <c r="G9">
-        <v>85.49223000000001</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>50.33829</v>
-      </c>
-      <c r="I9">
-        <v>33.96482</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>69.6288</v>
+      </c>
+      <c r="C10">
+        <v>96.17444999999999</v>
+      </c>
+      <c r="D10">
+        <v>84.00673</v>
+      </c>
+      <c r="E10">
+        <v>39.01345</v>
+      </c>
+      <c r="F10">
         <v>69.74128</v>
       </c>
-      <c r="C10">
-        <v>69.6288</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>99.69395</v>
       </c>
-      <c r="E10">
-        <v>96.17444999999999</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>104.0404</v>
       </c>
-      <c r="G10">
-        <v>84.00673</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>64.30493</v>
-      </c>
-      <c r="I10">
-        <v>39.01345</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:45</t>
+    <t xml:space="preserve">2026-08-02 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:42</t>
+    <t xml:space="preserve">2026-08-05 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:35</t>
+    <t xml:space="preserve">2026-08-16 09:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:47</t>
+    <t xml:space="preserve">2026-08-19 12:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:00</t>
+    <t xml:space="preserve">2026-08-28 11:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:25</t>
+    <t xml:space="preserve">2026-09-06 17:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
